--- a/www/download/COUNTRY.TUR.rpO1.xlsx
+++ b/www/download/COUNTRY.TUR.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Turquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.045627307212723</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.0789471581670156</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.146341531977318</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.255318926481855</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.398062215139079</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.592708488209772</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1.12520113062774</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1.5011408945586</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.48873766149879</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1.43231589474083</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1.34334577326075</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1.42411600761669</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.29760586993406</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>1.28747681169652</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1.54662060710616</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.586</t>
+          <t>1.36560903190815</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.195</t>
+          <t>1.31897906614767</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.204</t>
+          <t>1.30071780826927</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.779</t>
+          <t>1.29621568364929</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.048</t>
+          <t>1.41216989646994</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>1.38539430011869</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.524</t>
+          <t>1.33159297159862</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.354</t>
+          <t>1.36833851556321</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21.147</t>
+          <t>1.48093518557588</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21.732</t>
+          <t>1.3727217951801</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>21.956</t>
+          <t>1.44227238172727</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>21.093</t>
+          <t>1.43846945261545</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.738</t>
+          <t>1.43734204738779</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>21.194</t>
+          <t>1.4102193149497</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21.275</t>
+          <t>1.41904016222537</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.192</t>
+          <t>3.4533209931915</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.493</t>
+          <t>3.3551457343687</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.497</t>
+          <t>3.26753249161728</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.782</t>
+          <t>3.27262692817117</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.736</t>
+          <t>3.49593354289387</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.362</t>
+          <t>3.3730367180709</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11.051</t>
+          <t>3.28512379595882</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>3.34886454445263</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11.529</t>
+          <t>3.51932988663359</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11.812</t>
+          <t>3.29663644052985</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12.473</t>
+          <t>3.25026608242023</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12.479</t>
+          <t>3.14155497894185</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>12.535</t>
+          <t>3.09565225198206</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>12.937</t>
+          <t>3.00218412297836</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>12.768</t>
+          <t>2.99286356556872</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42695.615</t>
+          <t>4.46802140896115</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44294.708</t>
+          <t>4.36088894643524</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44759.107</t>
+          <t>4.24279867845913</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43374.73</t>
+          <t>4.19505905853879</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>43618.102</t>
+          <t>4.49201229476407</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42290.063</t>
+          <t>4.40184914241689</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>42188.186</t>
+          <t>4.39226256581069</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>41613.735</t>
+          <t>4.50585034289202</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41088.621</t>
+          <t>4.7447643978093</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>41681.976</t>
+          <t>4.49903518613867</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>42517.307</t>
+          <t>4.57997352079924</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>41001.067</t>
+          <t>4.5228265483182</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>39622.583</t>
+          <t>4.43569901900444</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>40258.093</t>
+          <t>4.3199774996099</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>40019.218</t>
+          <t>4.27372605067974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21136.968</t>
+          <t>8088444714142.26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21928.844</t>
+          <t>8316095341620.34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22158.416</t>
+          <t>9608939034190.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21473.141</t>
+          <t>11695257197036</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21239.635</t>
+          <t>13082443552747.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22266.289</t>
+          <t>16001421898540.3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21661.432</t>
+          <t>12578688444782.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22352.358</t>
+          <t>13498118996433.8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22401.434</t>
+          <t>16386375514601.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22654.767</t>
+          <t>17353148693171.3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>24154.349</t>
+          <t>19686747598400.8</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>24257.62</t>
+          <t>18046590357580.4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23949.859</t>
+          <t>16083694372739</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24573.739</t>
+          <t>13165708601825</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>24016.797</t>
+          <t>10473229145836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>839030571448.786</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>891283510869.975</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>1041131514513.86</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>1179633435871.59</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>1432163032015.57</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>1619182130640.14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>1270067683463.44</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>1225404817887.54</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>1500213152438.57</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>1589675934457.36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>1767571573239.07</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>1645535679020.59</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>1523636928008.68</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>1300167175503.85</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>1055404676746.37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>600135073.175992</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>577568525.030564</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>639415244.249118</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>741729079.671804</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>908139060.848565</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>1008949790.32184</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>1057607394.45519</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>968642544.891736</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>905367165.173959</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>764737019.57156</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>706144377.207181</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>603172936.966064</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>448997163.434485</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>320248046.34642</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>313373951.107708</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>173213.160081355</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>206577.303529011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>235019.362135253</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>265839.638960041</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>271845.574436207</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>278326.918335255</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>195515.849158371</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>217689.057139922</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>280361.32846478</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>361401.783050407</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>467395.380555382</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>489817.283367079</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>595421.658264791</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>676344.057806311</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>570099.778129574</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>363629.641062554</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>419927.346487464</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>475017.479933016</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>524680.734731301</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>547088.197591122</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>590015.973042383</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>438573.595073123</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>492057.086925439</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>627641.46026221</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>798879.150464548</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1014506.63617945</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>1078760.49548201</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>1282140.40636932</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>1398301.50551674</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>1158070.49517619</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>50285.1103942363</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>54077.1270264984</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>57121.9452990314</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>60402.6002907757</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>55702.0597379603</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>63.72</t>
+          <t>60834.3176809768</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>47348.8132081669</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>48630.5337446611</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>59459.8785830553</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>77499.3092627744</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>89080.2997914161</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>100673.708935067</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>114371.299749517</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>141163.370602808</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>119057.988207421</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.045627307212723</t>
+          <t>82326.0723024146</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.0789471581670156</t>
+          <t>84942.6253189743</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.146341531977318</t>
+          <t>99179.8816250821</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.255318926481855</t>
+          <t>109408.716930392</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.398062215139079</t>
+          <t>133396.051134015</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.592708488209772</t>
+          <t>142506.523849062</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.12520113062774</t>
+          <t>114923.164425477</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.5011408945586</t>
+          <t>106835.03464205</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.48873766149879</t>
+          <t>130121.764175191</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.43231589474083</t>
+          <t>134585.295009331</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.34334577326075</t>
+          <t>141707.943861357</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.42411600761669</t>
+          <t>131863.956792077</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.29760586993406</t>
+          <t>121548.701136723</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.28747681169652</t>
+          <t>100501.45000556</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.54662060710616</t>
+          <t>82661.4372485822</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>224030720158.644</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>186955832166.695</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>185013165072.641</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>161831818218.379</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>10546544227.9323</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>63296627340.6041</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>146804847778.916</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>264854533763.463</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>308528356559.881</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>250993079376.845</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>185284409939.955</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>184269806096.257</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>124782599699.103</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>-4800905298.06802</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>7748138203.12175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>269413310819.283</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>237944067273.322</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>227898378983.618</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>202307511409.761</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>61204436380.6997</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>120287299905.1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>212849235893.565</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>335838680827.377</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>405854813545.125</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>372910951232.22</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>305312734395.053</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>304450919295.072</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>264406073338.364</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>99750635596.9046</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>58638961812.1438</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>-45382590660.6389</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>-50988235106.6272</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-42885213910.9775</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>-40475693191.3821</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-50657892152.7673</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>-56990672564.4955</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-66044388114.6489</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>-70984147063.914</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-97326456985.2442</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>-121917871855.375</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-120028324455.098</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>-120181113198.814</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>-139623473639.261</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>-104551540894.973</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>-50890823609.022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>369024.778203918</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>369456.493428202</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>420252.770139092</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>461099.560624029</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>579889.953023703</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>607356.553173085</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>476613.855570284</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>449362.2525659</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>562653.001977848</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>565086.066428872</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>599024.001077557</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>546254.43849131</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>492332.917242152</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>396956.103267385</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>319621.315634095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>277684.603688467</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>289751.185294723</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>334869.883059349</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>393859.249900127</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>459272.371295285</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>539300.952586819</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>418698.13370817</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>428703.403611304</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>529742.37233567</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>554180.569325489</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>620259.273139306</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>589993.856051788</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>554491.157707662</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>462779.148251482</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>379269.522164788</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>136.56</t>
+          <t>28373.2571947244</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>35392.846337535</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>130.07</t>
+          <t>44182.5206399907</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>129.62</t>
+          <t>45068.0747185577</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>40944.055620681</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>138.54</t>
+          <t>42466.7268709208</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>133.16</t>
+          <t>42518.7329264322</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>42377.4179054965</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>148.09</t>
+          <t>53189.1647781823</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>137.27</t>
+          <t>71898.7903757085</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>144.23</t>
+          <t>83868.9361042611</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>143.85</t>
+          <t>96586.4794700815</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>143.73</t>
+          <t>119530.019278843</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>141.02</t>
+          <t>147548.299105145</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>117814.336000055</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>345.33</t>
+          <t>786926860996.12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>335.51</t>
+          <t>944014804970.595</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>326.75</t>
+          <t>1274532906133.6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>327.26</t>
+          <t>1511125062268</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>349.59</t>
+          <t>1602920792421.06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>337.3</t>
+          <t>1818958342851.51</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>328.51</t>
+          <t>1900169742386.15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>334.89</t>
+          <t>1726022106413.77</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>351.93</t>
+          <t>2040995707228.49</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>329.66</t>
+          <t>2332853067648.51</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>325.03</t>
+          <t>2545498928285.15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>314.16</t>
+          <t>2490334446012.24</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>309.57</t>
+          <t>2295021180105.34</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>300.22</t>
+          <t>1897827701177.04</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>299.29</t>
+          <t>1502760432602.37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>446.8</t>
+          <t>36307.7524217156</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>436.09</t>
+          <t>45857.6638916735</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>424.28</t>
+          <t>52401.3801911973</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>419.51</t>
+          <t>49810.6327445414</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>449.2</t>
+          <t>45700.1926724935</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>440.18</t>
+          <t>59045.7261993691</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>439.23</t>
+          <t>44933.3115517261</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>450.59</t>
+          <t>49556.9162526708</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>474.48</t>
+          <t>66806.2088307712</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>449.9</t>
+          <t>93903.9384528349</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>112728.182904063</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>452.28</t>
+          <t>135671.407790267</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>443.57</t>
+          <t>164454.831168997</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>192754.443914157</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>427.37</t>
+          <t>136836.012423562</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5716533.681</t>
+          <t>1300542409224.72</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6141175.742</t>
+          <t>1471545973867.94</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7100694.035</t>
+          <t>1733527003480.71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8577829.294</t>
+          <t>1850808997064.29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10126037.242</t>
+          <t>1805506815757.32</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11638114.557</t>
+          <t>2636656492600.4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9012058.63</t>
+          <t>2165126003534.41</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9154532.481</t>
+          <t>2329571143765.82</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11202461.948</t>
+          <t>2954618809016.47</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>12043452.133</t>
+          <t>3385922949983.01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13618412.601</t>
+          <t>3665932913667.57</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>12444448.657</t>
+          <t>3754364911334.14</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11499146.928</t>
+          <t>3333601229559.04</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9808048.791</t>
+          <t>2572682155430.75</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8068959.084</t>
+          <t>1791911795933.71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3760935.775</t>
+          <t>-7934.49522699114</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3876622.359</t>
+          <t>-10464.8175541385</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4411564.078</t>
+          <t>-8218.85955120662</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4971527.628</t>
+          <t>-4742.55802598362</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6225798.637</t>
+          <t>-4756.13705181254</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6900883.211</t>
+          <t>-16578.9993284484</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5267274.518</t>
+          <t>-2414.57862529393</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5154214.356</t>
+          <t>-7179.49834717424</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6486996.539</t>
+          <t>-13617.0440525889</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6674605.28</t>
+          <t>-22005.1480771263</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7471830.916</t>
+          <t>-28859.2467998021</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6816731.351</t>
+          <t>-39084.9283201859</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6171490.165</t>
+          <t>-44924.8118901542</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5135341.784</t>
+          <t>-45206.1448090123</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4080860.95</t>
+          <t>-19021.676423507</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8088444.714</t>
+          <t>-513615548228.596</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8316095.342</t>
+          <t>-527531168897.341</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9608939.034</t>
+          <t>-458994097347.103</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11695257.197</t>
+          <t>-339683934796.296</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13082443.553</t>
+          <t>-202586023336.259</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>16001421.899</t>
+          <t>-817698149748.889</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12578688.445</t>
+          <t>-264956261148.265</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13498118.996</t>
+          <t>-603549037352.052</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16386375.515</t>
+          <t>-913623101787.972</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>17353148.693</t>
+          <t>-1053069882334.5</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19686747.598</t>
+          <t>-1120433985382.42</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>18046590.358</t>
+          <t>-1264030465321.9</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>16083694.373</t>
+          <t>-1038580049453.69</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13165708.602</t>
+          <t>-674854454253.715</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10473229.146</t>
+          <t>-289151363331.347</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>131710.48886</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>143156.42783</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>148389.08056</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>148953.04224</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>131364.75843</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>136865.93355</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>99503.9513</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>112908.61759</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>147032.50953</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>184768.03532</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>229766.68346</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>248927.01838</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>301232.37276</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>340491.97154</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>276089.41882</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3852890.169</t>
+          <t>0.18089520317301</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4090985.181</t>
+          <t>0.176319413809432</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4754112.886</t>
+          <t>0.173604073574905</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5925628.187</t>
+          <t>0.160158023333973</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6500605.201</t>
+          <t>0.137410444688235</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7548315.045</t>
+          <t>0.144823242896442</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5607571.865</t>
+          <t>0.135239580115838</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5971650.192</t>
+          <t>0.154663284580822</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7319634.375</t>
+          <t>0.174595573165977</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7850322.387</t>
+          <t>0.174476143860154</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9069920.844</t>
+          <t>0.192828894034612</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8194156.071</t>
+          <t>0.192102753097173</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7469213.143</t>
+          <t>0.214193615790845</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6368117.852</t>
+          <t>0.184970723183781</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5155804.968</t>
+          <t>0.187392006324272</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>46762.503304833</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>55367.2707665812</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>63001.6664133908</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>64297.3387244751</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>73322.4637282348</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>73219.3651377562</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>53765.6546316908</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>53901.3390008949</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>69526.7132388374</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>89150.8864842486</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>111455.986843736</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>121229.481071189</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>149940.04512114</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>171134.668985618</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>142983.455042068</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>839030.571</t>
+          <t>70161.8268922823</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>891283.511</t>
+          <t>83196.192142393</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1041131.515</t>
+          <t>91495.0230014299</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1179633.436</t>
+          <t>97992.2643687726</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1432163.032</t>
+          <t>106370.615282295</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1619182.131</t>
+          <t>105618.88455691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1270067.683</t>
+          <t>76091.9902247633</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1225404.818</t>
+          <t>80176.3429900221</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1500213.152</t>
+          <t>102675.495454688</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1589675.934</t>
+          <t>131232.023706477</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1767571.573</t>
+          <t>165554.470880223</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1645535.679</t>
+          <t>175374.24917045</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1523636.928</t>
+          <t>215287.382182296</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1300167.176</t>
+          <t>244767.100246639</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1055404.677</t>
+          <t>205621.912332655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>499474.418550874</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>533756.468206192</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>550437.999649289</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>587776.21452127</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>559877.827440956</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>582562.337127349</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>490054.966676935</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>493727.862124982</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>595800.201780415</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>745855.383845791</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>850453.953280078</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>967933.017182874</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>1128625.07103967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>1439376.87839401</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>1175142.74268913</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>600.135</t>
+          <t>70161.8268922823</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>577.569</t>
+          <t>80194.8854862158</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>639.415</t>
+          <t>91844.8985943151</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>741.729</t>
+          <t>95943.6871792623</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>908.139</t>
+          <t>109779.848396017</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1008.95</t>
+          <t>116465.086951042</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1057.607</t>
+          <t>107483.918415649</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>968.643</t>
+          <t>108796.177636092</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>905.367</t>
+          <t>111828.597308575</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>764.737</t>
+          <t>124261.027676607</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>706.144</t>
+          <t>142161.686312851</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>603.173</t>
+          <t>149655.75467853</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>448.997</t>
+          <t>158716.65869586</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>320.248</t>
+          <t>164863.931029182</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>313.374</t>
+          <t>155485.163870762</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>46762.503304833</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>54694.8969687544</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>63962.6843634089</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>66460.2088113658</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>76509.3590790499</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>82970.0897450159</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>77029.3114614993</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76759.1111493038</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79672.9796598321</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>89362.7131902461</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>101562.088401659</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>108512.471041199</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>116135.362455626</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>121579.34525575</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>112804.144883177</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>140637.636817718</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>148188.754617607</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>152680.22428857</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>154539.676971227</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>132635.120977705</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>145202.88453309</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>113623.641135237</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>124992.106589978</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>163483.956305312</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>207633.280513523</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>253072.395029777</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>286616.30634955</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>356115.584587704</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>407405.952733361</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>339270.344477345</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3760935774973.36</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3876622359385</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4411564078161.87</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4971527628130.94</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6225798637198.39</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6900883210558.51</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5267274517516.98</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5154214355955.47</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6486996538793.87</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6674605280145</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7471830916046.14</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6816731351222.55</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6171490164593.38</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5135341784179.41</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4080860949630.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5716533681103.94</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6141175742056.26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7100694034572.07</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8577829293591.09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10126037242318.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>11638114556823.6</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9012058629934.64</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9154532480715.78</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11202461947782.4</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>12043452132581.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>13618412601046.6</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>12444448656895.8</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11499146927922</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9808048790823.35</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8068959084055.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3852890168650.75</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4090985180964.83</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4754112886393.83</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5925628186819.33</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6500605200925.6</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7548315044825.17</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5607571865265.25</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5971650191762</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7319634375455.61</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>7850322386814.2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>9069920843794.96</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>8194156070795.74</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7469213143011.88</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6368117851924.28</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5155804968015.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20586426.4895193</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21194652.7011088</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21204337.5465736</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>21778920.5046377</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22048000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21580000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21524000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21354000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21147000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>21732000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>21956000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>21092505.5053513</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20738197.1165437</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21193800.1698674</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>21275000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10191553.5137728</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10492770.9441879</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10497406.3031203</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10781896.2598939</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10736172.6216076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>11362161.4429044</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11051450.6784838</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11470065.2458555</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11529302.2804298</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>11811661.4028832</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>12473341.4731386</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>12479040.6647304</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>12535197.1165437</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12936800.1698674</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12767799.736805</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>42695615300.7843</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>44294708495.0847</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>44759106572.0011</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>43374729508.1917</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>43618102103.68</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42290062724</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>42188185937.76</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>41613735196.92</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>41088621000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>41681976000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>42517307455.04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>41001067162.3316</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>39622583151.2949</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>40258093077.2749</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40019217908</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21136968495.3787</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21928843884.9571</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22158415768.4229</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>21473141139.3276</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>21239635051.3431</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>22266289161.2901</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>21661431709.0623</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22352358238.851</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22401434330.8751</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>22654766570.73</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>24154349353.4859</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>24257620048.3281</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>23949858672.7149</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24573738602.1549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>24016797173.8145</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.196159356914378</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.205099460499401</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.224319242464061</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.213597988326195</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.229665835837909</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.236521133701938</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.24724104079533</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.258404667943629</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.273574401952396</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.253277563370187</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.261089069051448</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.268122020559815</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.274206541122043</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.278352587450768</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.282763303894695</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.224562015410273</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.233966072771193</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.231402199416765</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.244512742989034</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.241659550790121</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.249225344328062</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.254082731610233</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.257985594241123</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.264082328164442</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.267681917957441</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.274590947512387</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.277608235050942</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.286027236388928</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.290834914191311</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.295114194482208</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.579278627675349</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.560934466729406</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.544278558119174</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.54188926868477</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.52867461337197</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.51425352197</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.498676227594436</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.483609737815248</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.462343269883162</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.479040518672372</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.464319983436165</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.454269744389243</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.439766222489029</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.430812498357921</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.422122501623098</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0981629125401097</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.103058831998176</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.116034672772349</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.109895843177414</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.118474430887221</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.12379939560193</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.129729007768924</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.135899362035964</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.145703638911846</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.134170871828341</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.141029324945294</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.147403173888492</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.153634078765284</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.157996225929737</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.162358373094191</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.209931007375724</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.219362923238092</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.220271080232369</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.232052984924666</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.230352419444745</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.238998120408275</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.244037419803938</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.250117256113195</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.258896292167912</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.258298378554924</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.262183090935955</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.264231729578054</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.273623881762886</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.278684828921563</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.283745776080239</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.691906080084166</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.677578244763732</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.663694246995282</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.65805117189792</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.651173149668033</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.637202483989795</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.626233572427138</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.613983381850842</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.595400068920242</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.607530749616735</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.596787584118751</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.588365096533454</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.572742039471832</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.563318945148701</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.553895850825571</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>382448.20652</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>412167.12829</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>444490.62229</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>456989.47529</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>456770.98809</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>503027.80797</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>393452.21779</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>437574.62436</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>568297.69543</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>720650.84726</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>888719.53974</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>979252.31131</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1200909.03839</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1358920.18054</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1114299.58345</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>210799.46371</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>231384.94676</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>244175.24729</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>252531.94134</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>239005.73626</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>250821.76909</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>189715.63136</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>205168.44958</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>266159.45176</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>338865.30422</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>418626.86591</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>461990.55552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>571402.96677</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>652173.05298</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>544892.25681</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>22789.6723488672</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>24212.6998382652</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>25938.1133696823</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>27385.3760348765</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28274.6948310621</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29440.5458315137</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29622.8148884805</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30077.3742730262</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>30765.4799611517</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32111.1917932349</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33975.828948923</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>36018.8995046139</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>38130.594258392</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>39411.5783772959</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>40132.1943375151</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
